--- a/artfynd/A 54988-2025 artfynd.xlsx
+++ b/artfynd/A 54988-2025 artfynd.xlsx
@@ -2550,10 +2550,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130351283</v>
+        <v>130351258</v>
       </c>
       <c r="B21" t="n">
-        <v>91748</v>
+        <v>91728</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2561,19 +2561,23 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2581,10 +2585,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419527</v>
+        <v>419481</v>
       </c>
       <c r="R21" t="n">
-        <v>7019036</v>
+        <v>7019167</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2643,10 +2647,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130351267</v>
+        <v>130351283</v>
       </c>
       <c r="B22" t="n">
-        <v>57826</v>
+        <v>91748</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2654,23 +2658,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>419476</v>
+        <v>419527</v>
       </c>
       <c r="R22" t="n">
-        <v>7019228</v>
+        <v>7019036</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2714,11 +2714,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2745,10 +2740,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130351270</v>
+        <v>130351267</v>
       </c>
       <c r="B23" t="n">
-        <v>57985</v>
+        <v>57826</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2756,46 +2751,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gärdsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>419298</v>
+        <v>419476</v>
       </c>
       <c r="R23" t="n">
-        <v>7019139</v>
+        <v>7019228</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2832,7 +2815,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>obs i lämplig biotop</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2859,10 +2842,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130351258</v>
+        <v>130351270</v>
       </c>
       <c r="B24" t="n">
-        <v>91728</v>
+        <v>57985</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2870,34 +2853,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gärdsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>419481</v>
+        <v>419298</v>
       </c>
       <c r="R24" t="n">
-        <v>7019167</v>
+        <v>7019139</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2930,6 +2925,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>obs i lämplig biotop</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 54988-2025 artfynd.xlsx
+++ b/artfynd/A 54988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130351276</v>
       </c>
       <c r="B2" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>130351285</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130351278</v>
       </c>
       <c r="B6" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>130351284</v>
       </c>
       <c r="B7" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>130351275</v>
       </c>
       <c r="B8" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>130351280</v>
       </c>
       <c r="B9" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>130351286</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>130351273</v>
       </c>
       <c r="B12" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>130351279</v>
       </c>
       <c r="B13" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130351274</v>
+        <v>130351282</v>
       </c>
       <c r="B14" t="n">
-        <v>91724</v>
+        <v>91751</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1861,23 +1861,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1885,10 +1881,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>419551</v>
+        <v>419550</v>
       </c>
       <c r="R14" t="n">
-        <v>7019337</v>
+        <v>7019136</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,10 +1943,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130351265</v>
+        <v>130351274</v>
       </c>
       <c r="B15" t="n">
-        <v>57826</v>
+        <v>91727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1958,21 +1954,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1982,10 +1978,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>419404</v>
+        <v>419551</v>
       </c>
       <c r="R15" t="n">
-        <v>7019150</v>
+        <v>7019337</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2018,11 +2014,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2049,10 +2040,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130351282</v>
+        <v>130351265</v>
       </c>
       <c r="B16" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2060,19 +2051,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2080,10 +2075,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>419550</v>
+        <v>419404</v>
       </c>
       <c r="R16" t="n">
-        <v>7019136</v>
+        <v>7019150</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2116,6 +2111,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2550,10 +2550,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130351258</v>
+        <v>130351283</v>
       </c>
       <c r="B21" t="n">
-        <v>91728</v>
+        <v>91751</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2561,23 +2561,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2585,10 +2581,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419481</v>
+        <v>419527</v>
       </c>
       <c r="R21" t="n">
-        <v>7019167</v>
+        <v>7019036</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2647,10 +2643,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130351283</v>
+        <v>130351258</v>
       </c>
       <c r="B22" t="n">
-        <v>91748</v>
+        <v>91731</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2658,19 +2654,23 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>419527</v>
+        <v>419481</v>
       </c>
       <c r="R22" t="n">
-        <v>7019036</v>
+        <v>7019167</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3061,7 +3061,7 @@
         <v>130351272</v>
       </c>
       <c r="B26" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>130351277</v>
       </c>
       <c r="B27" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>130351281</v>
       </c>
       <c r="B28" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 54988-2025 artfynd.xlsx
+++ b/artfynd/A 54988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130351276</v>
       </c>
       <c r="B2" t="n">
-        <v>91727</v>
+        <v>91753</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130351259</v>
       </c>
       <c r="B3" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130351269</v>
       </c>
       <c r="B4" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>130351285</v>
       </c>
       <c r="B5" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130351278</v>
       </c>
       <c r="B6" t="n">
-        <v>91727</v>
+        <v>91753</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>130351284</v>
       </c>
       <c r="B7" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>130351275</v>
       </c>
       <c r="B8" t="n">
-        <v>91727</v>
+        <v>91753</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>130351280</v>
       </c>
       <c r="B9" t="n">
-        <v>91727</v>
+        <v>91753</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>130351286</v>
       </c>
       <c r="B10" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>130351266</v>
       </c>
       <c r="B11" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>130351273</v>
       </c>
       <c r="B12" t="n">
-        <v>91727</v>
+        <v>91753</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>130351279</v>
       </c>
       <c r="B13" t="n">
-        <v>91727</v>
+        <v>91753</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130351282</v>
+        <v>130351265</v>
       </c>
       <c r="B14" t="n">
-        <v>91751</v>
+        <v>57852</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1861,19 +1861,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1881,10 +1885,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>419550</v>
+        <v>419404</v>
       </c>
       <c r="R14" t="n">
-        <v>7019136</v>
+        <v>7019150</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1917,6 +1921,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1946,7 +1955,7 @@
         <v>130351274</v>
       </c>
       <c r="B15" t="n">
-        <v>91727</v>
+        <v>91753</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2040,10 +2049,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130351265</v>
+        <v>130351282</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>91777</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2051,23 +2060,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2075,10 +2080,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>419404</v>
+        <v>419550</v>
       </c>
       <c r="R16" t="n">
-        <v>7019150</v>
+        <v>7019136</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2111,11 +2116,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2145,7 +2145,7 @@
         <v>130351262</v>
       </c>
       <c r="B17" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>130351260</v>
       </c>
       <c r="B18" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>130351264</v>
       </c>
       <c r="B19" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>130351263</v>
       </c>
       <c r="B20" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130351283</v>
+        <v>130351258</v>
       </c>
       <c r="B21" t="n">
-        <v>91751</v>
+        <v>91757</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2561,19 +2561,23 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2581,10 +2585,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419527</v>
+        <v>419481</v>
       </c>
       <c r="R21" t="n">
-        <v>7019036</v>
+        <v>7019167</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2643,10 +2647,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130351258</v>
+        <v>130351270</v>
       </c>
       <c r="B22" t="n">
-        <v>91731</v>
+        <v>58011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2654,34 +2658,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gärdsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>419481</v>
+        <v>419298</v>
       </c>
       <c r="R22" t="n">
-        <v>7019167</v>
+        <v>7019139</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2714,6 +2730,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>obs i lämplig biotop</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2740,10 +2761,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130351267</v>
+        <v>130351283</v>
       </c>
       <c r="B23" t="n">
-        <v>57826</v>
+        <v>91777</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2751,23 +2772,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2775,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>419476</v>
+        <v>419527</v>
       </c>
       <c r="R23" t="n">
-        <v>7019228</v>
+        <v>7019036</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2811,11 +2828,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2842,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130351270</v>
+        <v>130351267</v>
       </c>
       <c r="B24" t="n">
-        <v>57985</v>
+        <v>57852</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2853,46 +2865,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gärdsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>419298</v>
+        <v>419476</v>
       </c>
       <c r="R24" t="n">
-        <v>7019139</v>
+        <v>7019228</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>obs i lämplig biotop</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2959,7 +2959,7 @@
         <v>130351268</v>
       </c>
       <c r="B25" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>130351272</v>
       </c>
       <c r="B26" t="n">
-        <v>92184</v>
+        <v>92210</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3155,10 +3155,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130351277</v>
+        <v>130351281</v>
       </c>
       <c r="B27" t="n">
-        <v>91727</v>
+        <v>91753</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>419689</v>
+        <v>419233</v>
       </c>
       <c r="R27" t="n">
-        <v>7018949</v>
+        <v>7019867</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3252,10 +3252,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130351281</v>
+        <v>130351277</v>
       </c>
       <c r="B28" t="n">
-        <v>91727</v>
+        <v>91753</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>419233</v>
+        <v>419689</v>
       </c>
       <c r="R28" t="n">
-        <v>7019867</v>
+        <v>7018949</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3352,7 +3352,7 @@
         <v>130351261</v>
       </c>
       <c r="B29" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 54988-2025 artfynd.xlsx
+++ b/artfynd/A 54988-2025 artfynd.xlsx
@@ -2550,10 +2550,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130351258</v>
+        <v>130351267</v>
       </c>
       <c r="B21" t="n">
-        <v>91757</v>
+        <v>57852</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2561,21 +2561,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419481</v>
+        <v>419476</v>
       </c>
       <c r="R21" t="n">
-        <v>7019167</v>
+        <v>7019228</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2621,6 +2621,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2761,10 +2766,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130351283</v>
+        <v>130351258</v>
       </c>
       <c r="B23" t="n">
-        <v>91777</v>
+        <v>91757</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2772,19 +2777,23 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2792,10 +2801,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>419527</v>
+        <v>419481</v>
       </c>
       <c r="R23" t="n">
-        <v>7019036</v>
+        <v>7019167</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2854,10 +2863,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130351267</v>
+        <v>130351283</v>
       </c>
       <c r="B24" t="n">
-        <v>57852</v>
+        <v>91777</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,23 +2874,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2889,10 +2894,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>419476</v>
+        <v>419527</v>
       </c>
       <c r="R24" t="n">
-        <v>7019228</v>
+        <v>7019036</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,11 +2930,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3155,7 +3155,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130351281</v>
+        <v>130351277</v>
       </c>
       <c r="B27" t="n">
         <v>91753</v>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>419233</v>
+        <v>419689</v>
       </c>
       <c r="R27" t="n">
-        <v>7019867</v>
+        <v>7018949</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130351277</v>
+        <v>130351281</v>
       </c>
       <c r="B28" t="n">
         <v>91753</v>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>419689</v>
+        <v>419233</v>
       </c>
       <c r="R28" t="n">
-        <v>7018949</v>
+        <v>7019867</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 54988-2025 artfynd.xlsx
+++ b/artfynd/A 54988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130351276</v>
       </c>
       <c r="B2" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130351278</v>
       </c>
       <c r="B6" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>130351284</v>
       </c>
       <c r="B7" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>130351275</v>
       </c>
       <c r="B8" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>130351280</v>
       </c>
       <c r="B9" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1656,10 +1656,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130351273</v>
+        <v>130351279</v>
       </c>
       <c r="B12" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>419486</v>
+        <v>419412</v>
       </c>
       <c r="R12" t="n">
-        <v>7019567</v>
+        <v>7019143</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130351279</v>
+        <v>130351273</v>
       </c>
       <c r="B13" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>419412</v>
+        <v>419486</v>
       </c>
       <c r="R13" t="n">
-        <v>7019143</v>
+        <v>7019567</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130351265</v>
+        <v>130351274</v>
       </c>
       <c r="B14" t="n">
-        <v>57852</v>
+        <v>91754</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1861,21 +1861,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>419404</v>
+        <v>419551</v>
       </c>
       <c r="R14" t="n">
-        <v>7019150</v>
+        <v>7019337</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1921,11 +1921,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1952,10 +1947,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130351274</v>
+        <v>130351282</v>
       </c>
       <c r="B15" t="n">
-        <v>91753</v>
+        <v>91778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1963,23 +1958,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -1987,10 +1978,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>419551</v>
+        <v>419550</v>
       </c>
       <c r="R15" t="n">
-        <v>7019337</v>
+        <v>7019136</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2049,10 +2040,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130351282</v>
+        <v>130351265</v>
       </c>
       <c r="B16" t="n">
-        <v>91777</v>
+        <v>57852</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2060,19 +2051,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2080,10 +2075,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>419550</v>
+        <v>419404</v>
       </c>
       <c r="R16" t="n">
-        <v>7019136</v>
+        <v>7019150</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2116,6 +2111,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2550,10 +2550,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130351267</v>
+        <v>130351270</v>
       </c>
       <c r="B21" t="n">
-        <v>57852</v>
+        <v>58011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2561,34 +2561,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gärdsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419476</v>
+        <v>419298</v>
       </c>
       <c r="R21" t="n">
-        <v>7019228</v>
+        <v>7019139</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2625,7 +2637,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>obs i lämplig biotop</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2652,10 +2664,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130351270</v>
+        <v>130351258</v>
       </c>
       <c r="B22" t="n">
-        <v>58011</v>
+        <v>91758</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2663,46 +2675,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gärdsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>419298</v>
+        <v>419481</v>
       </c>
       <c r="R22" t="n">
-        <v>7019139</v>
+        <v>7019167</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2735,11 +2735,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>obs i lämplig biotop</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2766,10 +2761,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130351258</v>
+        <v>130351283</v>
       </c>
       <c r="B23" t="n">
-        <v>91757</v>
+        <v>91778</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2777,23 +2772,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2801,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>419481</v>
+        <v>419527</v>
       </c>
       <c r="R23" t="n">
-        <v>7019167</v>
+        <v>7019036</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2863,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130351283</v>
+        <v>130351267</v>
       </c>
       <c r="B24" t="n">
-        <v>91777</v>
+        <v>57852</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2874,19 +2865,23 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2894,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>419527</v>
+        <v>419476</v>
       </c>
       <c r="R24" t="n">
-        <v>7019036</v>
+        <v>7019228</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2930,6 +2925,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,7 +3061,7 @@
         <v>130351272</v>
       </c>
       <c r="B26" t="n">
-        <v>92210</v>
+        <v>92211</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>130351277</v>
       </c>
       <c r="B27" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>130351281</v>
       </c>
       <c r="B28" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 54988-2025 artfynd.xlsx
+++ b/artfynd/A 54988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130351276</v>
       </c>
       <c r="B2" t="n">
-        <v>91754</v>
+        <v>91755</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130351278</v>
+        <v>130351284</v>
       </c>
       <c r="B6" t="n">
-        <v>91754</v>
+        <v>91779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,23 +1084,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1108,10 +1104,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>419628</v>
+        <v>419473</v>
       </c>
       <c r="R6" t="n">
-        <v>7019018</v>
+        <v>7019235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1166,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130351284</v>
+        <v>130351278</v>
       </c>
       <c r="B7" t="n">
-        <v>91778</v>
+        <v>91755</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,19 +1177,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>419473</v>
+        <v>419628</v>
       </c>
       <c r="R7" t="n">
-        <v>7019235</v>
+        <v>7019018</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,7 +1266,7 @@
         <v>130351275</v>
       </c>
       <c r="B8" t="n">
-        <v>91754</v>
+        <v>91755</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>130351280</v>
       </c>
       <c r="B9" t="n">
-        <v>91754</v>
+        <v>91755</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1656,10 +1656,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130351279</v>
+        <v>130351273</v>
       </c>
       <c r="B12" t="n">
-        <v>91754</v>
+        <v>91755</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>419412</v>
+        <v>419486</v>
       </c>
       <c r="R12" t="n">
-        <v>7019143</v>
+        <v>7019567</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130351273</v>
+        <v>130351279</v>
       </c>
       <c r="B13" t="n">
-        <v>91754</v>
+        <v>91755</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>419486</v>
+        <v>419412</v>
       </c>
       <c r="R13" t="n">
-        <v>7019567</v>
+        <v>7019143</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130351274</v>
+        <v>130351282</v>
       </c>
       <c r="B14" t="n">
-        <v>91754</v>
+        <v>91779</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1861,23 +1861,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1885,10 +1881,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>419551</v>
+        <v>419550</v>
       </c>
       <c r="R14" t="n">
-        <v>7019337</v>
+        <v>7019136</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,10 +1943,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130351282</v>
+        <v>130351274</v>
       </c>
       <c r="B15" t="n">
-        <v>91778</v>
+        <v>91755</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1958,19 +1954,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>419550</v>
+        <v>419551</v>
       </c>
       <c r="R15" t="n">
-        <v>7019136</v>
+        <v>7019337</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130351270</v>
+        <v>130351283</v>
       </c>
       <c r="B21" t="n">
-        <v>58011</v>
+        <v>91779</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2561,46 +2561,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gärdsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419298</v>
+        <v>419527</v>
       </c>
       <c r="R21" t="n">
-        <v>7019139</v>
+        <v>7019036</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2633,11 +2617,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>obs i lämplig biotop</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2664,10 +2643,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130351258</v>
+        <v>130351267</v>
       </c>
       <c r="B22" t="n">
-        <v>91758</v>
+        <v>57852</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2675,21 +2654,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2699,10 +2678,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>419481</v>
+        <v>419476</v>
       </c>
       <c r="R22" t="n">
-        <v>7019167</v>
+        <v>7019228</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2735,6 +2714,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2761,10 +2745,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130351283</v>
+        <v>130351270</v>
       </c>
       <c r="B23" t="n">
-        <v>91778</v>
+        <v>58011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2772,30 +2756,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gärdsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>419527</v>
+        <v>419298</v>
       </c>
       <c r="R23" t="n">
-        <v>7019036</v>
+        <v>7019139</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2828,6 +2828,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>obs i lämplig biotop</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2854,10 +2859,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130351267</v>
+        <v>130351258</v>
       </c>
       <c r="B24" t="n">
-        <v>57852</v>
+        <v>91759</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2870,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2894,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>419476</v>
+        <v>419481</v>
       </c>
       <c r="R24" t="n">
-        <v>7019228</v>
+        <v>7019167</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,11 +2930,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,7 +3061,7 @@
         <v>130351272</v>
       </c>
       <c r="B26" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>130351277</v>
       </c>
       <c r="B27" t="n">
-        <v>91754</v>
+        <v>91755</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>130351281</v>
       </c>
       <c r="B28" t="n">
-        <v>91754</v>
+        <v>91755</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 54988-2025 artfynd.xlsx
+++ b/artfynd/A 54988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130351276</v>
       </c>
       <c r="B2" t="n">
-        <v>91755</v>
+        <v>91757</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130351259</v>
       </c>
       <c r="B3" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130351269</v>
       </c>
       <c r="B4" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>130351285</v>
       </c>
       <c r="B5" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130351284</v>
+        <v>130351278</v>
       </c>
       <c r="B6" t="n">
-        <v>91779</v>
+        <v>91757</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,19 +1084,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1104,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>419473</v>
+        <v>419628</v>
       </c>
       <c r="R6" t="n">
-        <v>7019235</v>
+        <v>7019018</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130351278</v>
+        <v>130351284</v>
       </c>
       <c r="B7" t="n">
-        <v>91755</v>
+        <v>91781</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,23 +1181,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>419628</v>
+        <v>419473</v>
       </c>
       <c r="R7" t="n">
-        <v>7019018</v>
+        <v>7019235</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,7 +1266,7 @@
         <v>130351275</v>
       </c>
       <c r="B8" t="n">
-        <v>91755</v>
+        <v>91757</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>130351280</v>
       </c>
       <c r="B9" t="n">
-        <v>91755</v>
+        <v>91757</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>130351286</v>
       </c>
       <c r="B10" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>130351266</v>
       </c>
       <c r="B11" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>130351273</v>
       </c>
       <c r="B12" t="n">
-        <v>91755</v>
+        <v>91757</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>130351279</v>
       </c>
       <c r="B13" t="n">
-        <v>91755</v>
+        <v>91757</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130351282</v>
+        <v>130351274</v>
       </c>
       <c r="B14" t="n">
-        <v>91779</v>
+        <v>91757</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1861,19 +1861,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1881,10 +1885,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>419550</v>
+        <v>419551</v>
       </c>
       <c r="R14" t="n">
-        <v>7019136</v>
+        <v>7019337</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1943,10 +1947,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130351274</v>
+        <v>130351282</v>
       </c>
       <c r="B15" t="n">
-        <v>91755</v>
+        <v>91781</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1954,23 +1958,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>419551</v>
+        <v>419550</v>
       </c>
       <c r="R15" t="n">
-        <v>7019337</v>
+        <v>7019136</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2043,7 +2043,7 @@
         <v>130351265</v>
       </c>
       <c r="B16" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>130351262</v>
       </c>
       <c r="B17" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>130351260</v>
       </c>
       <c r="B18" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>130351264</v>
       </c>
       <c r="B19" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>130351263</v>
       </c>
       <c r="B20" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>130351283</v>
       </c>
       <c r="B21" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>130351267</v>
       </c>
       <c r="B22" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>130351270</v>
       </c>
       <c r="B23" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>130351258</v>
       </c>
       <c r="B24" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>130351268</v>
       </c>
       <c r="B25" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>130351272</v>
       </c>
       <c r="B26" t="n">
-        <v>92212</v>
+        <v>92214</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>130351277</v>
       </c>
       <c r="B27" t="n">
-        <v>91755</v>
+        <v>91757</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>130351281</v>
       </c>
       <c r="B28" t="n">
-        <v>91755</v>
+        <v>91757</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>130351261</v>
       </c>
       <c r="B29" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 54988-2025 artfynd.xlsx
+++ b/artfynd/A 54988-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130351276</v>
+        <v>130351259</v>
       </c>
       <c r="B2" t="n">
-        <v>91757</v>
+        <v>57854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419580</v>
+        <v>419346</v>
       </c>
       <c r="R2" t="n">
-        <v>7019107</v>
+        <v>7019843</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130351259</v>
+        <v>130351276</v>
       </c>
       <c r="B3" t="n">
-        <v>57854</v>
+        <v>91757</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419346</v>
+        <v>419580</v>
       </c>
       <c r="R3" t="n">
-        <v>7019843</v>
+        <v>7019107</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2550,10 +2550,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130351283</v>
+        <v>130351258</v>
       </c>
       <c r="B21" t="n">
-        <v>91781</v>
+        <v>91761</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2561,19 +2561,23 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2581,10 +2585,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419527</v>
+        <v>419481</v>
       </c>
       <c r="R21" t="n">
-        <v>7019036</v>
+        <v>7019167</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2643,10 +2647,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130351267</v>
+        <v>130351283</v>
       </c>
       <c r="B22" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2654,23 +2658,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>419476</v>
+        <v>419527</v>
       </c>
       <c r="R22" t="n">
-        <v>7019228</v>
+        <v>7019036</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2714,11 +2714,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2745,10 +2740,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130351270</v>
+        <v>130351267</v>
       </c>
       <c r="B23" t="n">
-        <v>58013</v>
+        <v>57854</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2756,46 +2751,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gärdsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>419298</v>
+        <v>419476</v>
       </c>
       <c r="R23" t="n">
-        <v>7019139</v>
+        <v>7019228</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2832,7 +2815,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>obs i lämplig biotop</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2859,10 +2842,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130351258</v>
+        <v>130351270</v>
       </c>
       <c r="B24" t="n">
-        <v>91761</v>
+        <v>58013</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2870,34 +2853,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gärdsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>419481</v>
+        <v>419298</v>
       </c>
       <c r="R24" t="n">
-        <v>7019167</v>
+        <v>7019139</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2930,6 +2925,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>obs i lämplig biotop</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,7 +3061,7 @@
         <v>130351272</v>
       </c>
       <c r="B26" t="n">
-        <v>92214</v>
+        <v>92220</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 54988-2025 artfynd.xlsx
+++ b/artfynd/A 54988-2025 artfynd.xlsx
@@ -1457,10 +1457,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130351286</v>
+        <v>130351266</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1468,21 +1468,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>419591</v>
+        <v>419477</v>
       </c>
       <c r="R10" t="n">
-        <v>7019120</v>
+        <v>7019181</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1528,6 +1528,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1554,10 +1559,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130351266</v>
+        <v>130351286</v>
       </c>
       <c r="B11" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1565,21 +1570,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1589,10 +1594,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>419477</v>
+        <v>419591</v>
       </c>
       <c r="R11" t="n">
-        <v>7019181</v>
+        <v>7019120</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1625,11 +1630,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 54988-2025 artfynd.xlsx
+++ b/artfynd/A 54988-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130351259</v>
+        <v>130351276</v>
       </c>
       <c r="B2" t="n">
-        <v>57854</v>
+        <v>91757</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419346</v>
+        <v>419580</v>
       </c>
       <c r="R2" t="n">
-        <v>7019843</v>
+        <v>7019107</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130351276</v>
+        <v>130351259</v>
       </c>
       <c r="B3" t="n">
-        <v>91757</v>
+        <v>57854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419580</v>
+        <v>419346</v>
       </c>
       <c r="R3" t="n">
-        <v>7019107</v>
+        <v>7019843</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130351278</v>
+        <v>130351284</v>
       </c>
       <c r="B6" t="n">
-        <v>91757</v>
+        <v>91781</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,23 +1084,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1108,10 +1104,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>419628</v>
+        <v>419473</v>
       </c>
       <c r="R6" t="n">
-        <v>7019018</v>
+        <v>7019235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1166,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130351284</v>
+        <v>130351278</v>
       </c>
       <c r="B7" t="n">
-        <v>91781</v>
+        <v>91757</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,19 +1177,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>419473</v>
+        <v>419628</v>
       </c>
       <c r="R7" t="n">
-        <v>7019235</v>
+        <v>7019018</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2346,7 +2346,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130351264</v>
+        <v>130351263</v>
       </c>
       <c r="B19" t="n">
         <v>57854</v>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>419527</v>
+        <v>419602</v>
       </c>
       <c r="R19" t="n">
-        <v>7019036</v>
+        <v>7019089</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2448,7 +2448,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130351263</v>
+        <v>130351264</v>
       </c>
       <c r="B20" t="n">
         <v>57854</v>
@@ -2483,10 +2483,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>419602</v>
+        <v>419527</v>
       </c>
       <c r="R20" t="n">
-        <v>7019089</v>
+        <v>7019036</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 54988-2025 artfynd.xlsx
+++ b/artfynd/A 54988-2025 artfynd.xlsx
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130351284</v>
+        <v>130351278</v>
       </c>
       <c r="B6" t="n">
-        <v>91781</v>
+        <v>91757</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,19 +1084,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1104,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>419473</v>
+        <v>419628</v>
       </c>
       <c r="R6" t="n">
-        <v>7019235</v>
+        <v>7019018</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130351278</v>
+        <v>130351284</v>
       </c>
       <c r="B7" t="n">
-        <v>91757</v>
+        <v>91781</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,23 +1181,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>419628</v>
+        <v>419473</v>
       </c>
       <c r="R7" t="n">
-        <v>7019018</v>
+        <v>7019235</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130351266</v>
+        <v>130351286</v>
       </c>
       <c r="B10" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1468,21 +1468,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>419477</v>
+        <v>419591</v>
       </c>
       <c r="R10" t="n">
-        <v>7019181</v>
+        <v>7019120</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1528,11 +1528,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1559,10 +1554,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130351286</v>
+        <v>130351266</v>
       </c>
       <c r="B11" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1570,21 +1565,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1594,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>419591</v>
+        <v>419477</v>
       </c>
       <c r="R11" t="n">
-        <v>7019120</v>
+        <v>7019181</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1630,6 +1625,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1947,10 +1947,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130351282</v>
+        <v>130351265</v>
       </c>
       <c r="B15" t="n">
-        <v>91781</v>
+        <v>57854</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1958,19 +1958,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -1978,10 +1982,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>419550</v>
+        <v>419404</v>
       </c>
       <c r="R15" t="n">
-        <v>7019136</v>
+        <v>7019150</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2014,6 +2018,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2040,10 +2049,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130351265</v>
+        <v>130351282</v>
       </c>
       <c r="B16" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2051,23 +2060,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2075,10 +2080,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>419404</v>
+        <v>419550</v>
       </c>
       <c r="R16" t="n">
-        <v>7019150</v>
+        <v>7019136</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2111,11 +2116,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2346,7 +2346,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130351263</v>
+        <v>130351264</v>
       </c>
       <c r="B19" t="n">
         <v>57854</v>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>419602</v>
+        <v>419527</v>
       </c>
       <c r="R19" t="n">
-        <v>7019089</v>
+        <v>7019036</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2448,7 +2448,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130351264</v>
+        <v>130351263</v>
       </c>
       <c r="B20" t="n">
         <v>57854</v>
@@ -2483,10 +2483,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>419527</v>
+        <v>419602</v>
       </c>
       <c r="R20" t="n">
-        <v>7019036</v>
+        <v>7019089</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130351258</v>
+        <v>130351267</v>
       </c>
       <c r="B21" t="n">
-        <v>91761</v>
+        <v>57854</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2561,21 +2561,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419481</v>
+        <v>419476</v>
       </c>
       <c r="R21" t="n">
-        <v>7019167</v>
+        <v>7019228</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2621,6 +2621,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2647,10 +2652,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130351283</v>
+        <v>130351258</v>
       </c>
       <c r="B22" t="n">
-        <v>91781</v>
+        <v>91761</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2658,19 +2663,23 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2678,10 +2687,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>419527</v>
+        <v>419481</v>
       </c>
       <c r="R22" t="n">
-        <v>7019036</v>
+        <v>7019167</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2740,10 +2749,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130351267</v>
+        <v>130351283</v>
       </c>
       <c r="B23" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2751,23 +2760,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2775,10 +2780,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>419476</v>
+        <v>419527</v>
       </c>
       <c r="R23" t="n">
-        <v>7019228</v>
+        <v>7019036</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2811,11 +2816,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 54988-2025 artfynd.xlsx
+++ b/artfynd/A 54988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130351276</v>
       </c>
       <c r="B2" t="n">
-        <v>91757</v>
+        <v>91770</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130351259</v>
       </c>
       <c r="B3" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130351269</v>
       </c>
       <c r="B4" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>130351285</v>
       </c>
       <c r="B5" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130351278</v>
+        <v>130351284</v>
       </c>
       <c r="B6" t="n">
-        <v>91757</v>
+        <v>91794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,23 +1084,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1108,10 +1104,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>419628</v>
+        <v>419473</v>
       </c>
       <c r="R6" t="n">
-        <v>7019018</v>
+        <v>7019235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1166,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130351284</v>
+        <v>130351278</v>
       </c>
       <c r="B7" t="n">
-        <v>91781</v>
+        <v>91770</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,19 +1177,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>419473</v>
+        <v>419628</v>
       </c>
       <c r="R7" t="n">
-        <v>7019235</v>
+        <v>7019018</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,7 +1266,7 @@
         <v>130351275</v>
       </c>
       <c r="B8" t="n">
-        <v>91757</v>
+        <v>91770</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>130351280</v>
       </c>
       <c r="B9" t="n">
-        <v>91757</v>
+        <v>91770</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>130351286</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>130351266</v>
       </c>
       <c r="B11" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>130351273</v>
       </c>
       <c r="B12" t="n">
-        <v>91757</v>
+        <v>91770</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>130351279</v>
       </c>
       <c r="B13" t="n">
-        <v>91757</v>
+        <v>91770</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>130351274</v>
       </c>
       <c r="B14" t="n">
-        <v>91757</v>
+        <v>91770</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>130351265</v>
       </c>
       <c r="B15" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>130351282</v>
       </c>
       <c r="B16" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>130351262</v>
       </c>
       <c r="B17" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>130351260</v>
       </c>
       <c r="B18" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>130351264</v>
       </c>
       <c r="B19" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>130351263</v>
       </c>
       <c r="B20" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130351267</v>
+        <v>130351283</v>
       </c>
       <c r="B21" t="n">
-        <v>57854</v>
+        <v>91794</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2561,23 +2561,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2585,10 +2581,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419476</v>
+        <v>419527</v>
       </c>
       <c r="R21" t="n">
-        <v>7019228</v>
+        <v>7019036</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2621,11 +2617,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2655,7 +2646,7 @@
         <v>130351258</v>
       </c>
       <c r="B22" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2749,10 +2740,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130351283</v>
+        <v>130351267</v>
       </c>
       <c r="B23" t="n">
-        <v>91781</v>
+        <v>57862</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2760,19 +2751,23 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2780,10 +2775,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>419527</v>
+        <v>419476</v>
       </c>
       <c r="R23" t="n">
-        <v>7019036</v>
+        <v>7019228</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2816,6 +2811,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2845,7 +2845,7 @@
         <v>130351270</v>
       </c>
       <c r="B24" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>130351268</v>
       </c>
       <c r="B25" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>130351272</v>
       </c>
       <c r="B26" t="n">
-        <v>92220</v>
+        <v>92233</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>130351277</v>
       </c>
       <c r="B27" t="n">
-        <v>91757</v>
+        <v>91770</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>130351281</v>
       </c>
       <c r="B28" t="n">
-        <v>91757</v>
+        <v>91770</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>130351261</v>
       </c>
       <c r="B29" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 54988-2025 artfynd.xlsx
+++ b/artfynd/A 54988-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130351276</v>
+        <v>130351259</v>
       </c>
       <c r="B2" t="n">
-        <v>91770</v>
+        <v>57863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419580</v>
+        <v>419346</v>
       </c>
       <c r="R2" t="n">
-        <v>7019107</v>
+        <v>7019843</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130351259</v>
+        <v>130351276</v>
       </c>
       <c r="B3" t="n">
-        <v>57862</v>
+        <v>91771</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419346</v>
+        <v>419580</v>
       </c>
       <c r="R3" t="n">
-        <v>7019843</v>
+        <v>7019107</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,7 +877,7 @@
         <v>130351269</v>
       </c>
       <c r="B4" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>130351285</v>
       </c>
       <c r="B5" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130351284</v>
       </c>
       <c r="B6" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>130351278</v>
       </c>
       <c r="B7" t="n">
-        <v>91770</v>
+        <v>91771</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>130351275</v>
       </c>
       <c r="B8" t="n">
-        <v>91770</v>
+        <v>91771</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>130351280</v>
       </c>
       <c r="B9" t="n">
-        <v>91770</v>
+        <v>91771</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>130351286</v>
       </c>
       <c r="B10" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>130351266</v>
       </c>
       <c r="B11" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>130351273</v>
       </c>
       <c r="B12" t="n">
-        <v>91770</v>
+        <v>91771</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>130351279</v>
       </c>
       <c r="B13" t="n">
-        <v>91770</v>
+        <v>91771</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130351274</v>
+        <v>130351282</v>
       </c>
       <c r="B14" t="n">
-        <v>91770</v>
+        <v>91795</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1861,23 +1861,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1885,10 +1881,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>419551</v>
+        <v>419550</v>
       </c>
       <c r="R14" t="n">
-        <v>7019337</v>
+        <v>7019136</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,10 +1943,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130351265</v>
+        <v>130351274</v>
       </c>
       <c r="B15" t="n">
-        <v>57862</v>
+        <v>91771</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1958,21 +1954,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1982,10 +1978,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>419404</v>
+        <v>419551</v>
       </c>
       <c r="R15" t="n">
-        <v>7019150</v>
+        <v>7019337</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2018,11 +2014,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2049,10 +2040,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130351282</v>
+        <v>130351265</v>
       </c>
       <c r="B16" t="n">
-        <v>91794</v>
+        <v>57863</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2060,19 +2051,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2080,10 +2075,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>419550</v>
+        <v>419404</v>
       </c>
       <c r="R16" t="n">
-        <v>7019136</v>
+        <v>7019150</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2116,6 +2111,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2145,7 +2145,7 @@
         <v>130351262</v>
       </c>
       <c r="B17" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>130351260</v>
       </c>
       <c r="B18" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>130351264</v>
       </c>
       <c r="B19" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>130351263</v>
       </c>
       <c r="B20" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130351283</v>
+        <v>130351267</v>
       </c>
       <c r="B21" t="n">
-        <v>91794</v>
+        <v>57863</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2561,19 +2561,23 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2581,10 +2585,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419527</v>
+        <v>419476</v>
       </c>
       <c r="R21" t="n">
-        <v>7019036</v>
+        <v>7019228</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2617,6 +2621,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2646,7 +2655,7 @@
         <v>130351258</v>
       </c>
       <c r="B22" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2740,10 +2749,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130351267</v>
+        <v>130351270</v>
       </c>
       <c r="B23" t="n">
-        <v>57862</v>
+        <v>58022</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2751,34 +2760,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gärdsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>419476</v>
+        <v>419298</v>
       </c>
       <c r="R23" t="n">
-        <v>7019228</v>
+        <v>7019139</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2815,7 +2836,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>obs i lämplig biotop</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2842,10 +2863,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130351270</v>
+        <v>130351283</v>
       </c>
       <c r="B24" t="n">
-        <v>58021</v>
+        <v>91795</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2853,46 +2874,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gärdsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>419298</v>
+        <v>419527</v>
       </c>
       <c r="R24" t="n">
-        <v>7019139</v>
+        <v>7019036</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,11 +2930,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>obs i lämplig biotop</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2959,7 +2959,7 @@
         <v>130351268</v>
       </c>
       <c r="B25" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>130351272</v>
       </c>
       <c r="B26" t="n">
-        <v>92233</v>
+        <v>92234</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>130351277</v>
       </c>
       <c r="B27" t="n">
-        <v>91770</v>
+        <v>91771</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>130351281</v>
       </c>
       <c r="B28" t="n">
-        <v>91770</v>
+        <v>91771</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>130351261</v>
       </c>
       <c r="B29" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 54988-2025 artfynd.xlsx
+++ b/artfynd/A 54988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130351259</v>
       </c>
       <c r="B2" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130351276</v>
       </c>
       <c r="B3" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130351269</v>
       </c>
       <c r="B4" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>130351285</v>
       </c>
       <c r="B5" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130351284</v>
+        <v>130351278</v>
       </c>
       <c r="B6" t="n">
-        <v>91795</v>
+        <v>91772</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,19 +1084,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1104,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>419473</v>
+        <v>419628</v>
       </c>
       <c r="R6" t="n">
-        <v>7019235</v>
+        <v>7019018</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130351278</v>
+        <v>130351284</v>
       </c>
       <c r="B7" t="n">
-        <v>91771</v>
+        <v>91796</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,23 +1181,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>419628</v>
+        <v>419473</v>
       </c>
       <c r="R7" t="n">
-        <v>7019018</v>
+        <v>7019235</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,7 +1266,7 @@
         <v>130351275</v>
       </c>
       <c r="B8" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>130351280</v>
       </c>
       <c r="B9" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>130351286</v>
       </c>
       <c r="B10" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>130351266</v>
       </c>
       <c r="B11" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>130351273</v>
       </c>
       <c r="B12" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>130351279</v>
       </c>
       <c r="B13" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130351282</v>
+        <v>130351265</v>
       </c>
       <c r="B14" t="n">
-        <v>91795</v>
+        <v>57864</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1861,19 +1861,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1881,10 +1885,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>419550</v>
+        <v>419404</v>
       </c>
       <c r="R14" t="n">
-        <v>7019136</v>
+        <v>7019150</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1917,6 +1921,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1946,7 +1955,7 @@
         <v>130351274</v>
       </c>
       <c r="B15" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2040,10 +2049,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130351265</v>
+        <v>130351282</v>
       </c>
       <c r="B16" t="n">
-        <v>57863</v>
+        <v>91796</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2051,23 +2060,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2075,10 +2080,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>419404</v>
+        <v>419550</v>
       </c>
       <c r="R16" t="n">
-        <v>7019150</v>
+        <v>7019136</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2111,11 +2116,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2145,7 +2145,7 @@
         <v>130351262</v>
       </c>
       <c r="B17" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>130351260</v>
       </c>
       <c r="B18" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>130351264</v>
       </c>
       <c r="B19" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>130351263</v>
       </c>
       <c r="B20" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>130351267</v>
       </c>
       <c r="B21" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>130351258</v>
       </c>
       <c r="B22" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2749,10 +2749,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130351270</v>
+        <v>130351283</v>
       </c>
       <c r="B23" t="n">
-        <v>58022</v>
+        <v>91796</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2760,46 +2760,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gärdsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>419298</v>
+        <v>419527</v>
       </c>
       <c r="R23" t="n">
-        <v>7019139</v>
+        <v>7019036</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2832,11 +2816,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>obs i lämplig biotop</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2863,10 +2842,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130351283</v>
+        <v>130351270</v>
       </c>
       <c r="B24" t="n">
-        <v>91795</v>
+        <v>58023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2874,30 +2853,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gärdsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>419527</v>
+        <v>419298</v>
       </c>
       <c r="R24" t="n">
-        <v>7019036</v>
+        <v>7019139</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2930,6 +2925,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>obs i lämplig biotop</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2959,7 +2959,7 @@
         <v>130351268</v>
       </c>
       <c r="B25" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>130351272</v>
       </c>
       <c r="B26" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>130351277</v>
       </c>
       <c r="B27" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>130351281</v>
       </c>
       <c r="B28" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>130351261</v>
       </c>
       <c r="B29" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 54988-2025 artfynd.xlsx
+++ b/artfynd/A 54988-2025 artfynd.xlsx
@@ -1656,7 +1656,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130351273</v>
+        <v>130351279</v>
       </c>
       <c r="B12" t="n">
         <v>91772</v>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>419486</v>
+        <v>419412</v>
       </c>
       <c r="R12" t="n">
-        <v>7019567</v>
+        <v>7019143</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130351279</v>
+        <v>130351273</v>
       </c>
       <c r="B13" t="n">
         <v>91772</v>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>419412</v>
+        <v>419486</v>
       </c>
       <c r="R13" t="n">
-        <v>7019143</v>
+        <v>7019567</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130351265</v>
+        <v>130351274</v>
       </c>
       <c r="B14" t="n">
-        <v>57864</v>
+        <v>91772</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1861,21 +1861,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>419404</v>
+        <v>419551</v>
       </c>
       <c r="R14" t="n">
-        <v>7019150</v>
+        <v>7019337</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1921,11 +1921,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1952,10 +1947,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130351274</v>
+        <v>130351282</v>
       </c>
       <c r="B15" t="n">
-        <v>91772</v>
+        <v>91796</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1963,23 +1958,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -1987,10 +1978,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>419551</v>
+        <v>419550</v>
       </c>
       <c r="R15" t="n">
-        <v>7019337</v>
+        <v>7019136</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2049,10 +2040,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130351282</v>
+        <v>130351265</v>
       </c>
       <c r="B16" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2060,19 +2051,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2080,10 +2075,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>419550</v>
+        <v>419404</v>
       </c>
       <c r="R16" t="n">
-        <v>7019136</v>
+        <v>7019150</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2116,6 +2111,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2550,10 +2550,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130351267</v>
+        <v>130351283</v>
       </c>
       <c r="B21" t="n">
-        <v>57864</v>
+        <v>91796</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2561,23 +2561,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2585,10 +2581,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419476</v>
+        <v>419527</v>
       </c>
       <c r="R21" t="n">
-        <v>7019228</v>
+        <v>7019036</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2621,11 +2617,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2652,10 +2643,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130351258</v>
+        <v>130351267</v>
       </c>
       <c r="B22" t="n">
-        <v>91776</v>
+        <v>57864</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2663,21 +2654,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2687,10 +2678,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>419481</v>
+        <v>419476</v>
       </c>
       <c r="R22" t="n">
-        <v>7019167</v>
+        <v>7019228</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2723,6 +2714,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2749,10 +2745,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130351283</v>
+        <v>130351258</v>
       </c>
       <c r="B23" t="n">
-        <v>91796</v>
+        <v>91776</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2760,19 +2756,23 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>419527</v>
+        <v>419481</v>
       </c>
       <c r="R23" t="n">
-        <v>7019036</v>
+        <v>7019167</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3155,7 +3155,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130351277</v>
+        <v>130351281</v>
       </c>
       <c r="B27" t="n">
         <v>91772</v>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>419689</v>
+        <v>419233</v>
       </c>
       <c r="R27" t="n">
-        <v>7018949</v>
+        <v>7019867</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130351281</v>
+        <v>130351277</v>
       </c>
       <c r="B28" t="n">
         <v>91772</v>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>419233</v>
+        <v>419689</v>
       </c>
       <c r="R28" t="n">
-        <v>7019867</v>
+        <v>7018949</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 54988-2025 artfynd.xlsx
+++ b/artfynd/A 54988-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130351259</v>
+        <v>130351276</v>
       </c>
       <c r="B2" t="n">
-        <v>57864</v>
+        <v>91772</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419346</v>
+        <v>419580</v>
       </c>
       <c r="R2" t="n">
-        <v>7019843</v>
+        <v>7019107</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130351276</v>
+        <v>130351259</v>
       </c>
       <c r="B3" t="n">
-        <v>91772</v>
+        <v>57864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419580</v>
+        <v>419346</v>
       </c>
       <c r="R3" t="n">
-        <v>7019107</v>
+        <v>7019843</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130351278</v>
+        <v>130351284</v>
       </c>
       <c r="B6" t="n">
-        <v>91772</v>
+        <v>91796</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,23 +1084,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1108,10 +1104,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>419628</v>
+        <v>419473</v>
       </c>
       <c r="R6" t="n">
-        <v>7019018</v>
+        <v>7019235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1166,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130351284</v>
+        <v>130351278</v>
       </c>
       <c r="B7" t="n">
-        <v>91796</v>
+        <v>91772</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,19 +1177,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>419473</v>
+        <v>419628</v>
       </c>
       <c r="R7" t="n">
-        <v>7019235</v>
+        <v>7019018</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130351274</v>
+        <v>130351282</v>
       </c>
       <c r="B14" t="n">
-        <v>91772</v>
+        <v>91796</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1861,23 +1861,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1885,10 +1881,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>419551</v>
+        <v>419550</v>
       </c>
       <c r="R14" t="n">
-        <v>7019337</v>
+        <v>7019136</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,10 +1943,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130351282</v>
+        <v>130351274</v>
       </c>
       <c r="B15" t="n">
-        <v>91796</v>
+        <v>91772</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1958,19 +1954,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>419550</v>
+        <v>419551</v>
       </c>
       <c r="R15" t="n">
-        <v>7019136</v>
+        <v>7019337</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2346,7 +2346,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130351264</v>
+        <v>130351263</v>
       </c>
       <c r="B19" t="n">
         <v>57864</v>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>419527</v>
+        <v>419602</v>
       </c>
       <c r="R19" t="n">
-        <v>7019036</v>
+        <v>7019089</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2448,7 +2448,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130351263</v>
+        <v>130351264</v>
       </c>
       <c r="B20" t="n">
         <v>57864</v>
@@ -2483,10 +2483,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>419602</v>
+        <v>419527</v>
       </c>
       <c r="R20" t="n">
-        <v>7019089</v>
+        <v>7019036</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2745,10 +2745,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130351258</v>
+        <v>130351270</v>
       </c>
       <c r="B23" t="n">
-        <v>91776</v>
+        <v>58023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2756,34 +2756,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gärdsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>419481</v>
+        <v>419298</v>
       </c>
       <c r="R23" t="n">
-        <v>7019167</v>
+        <v>7019139</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2816,6 +2828,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>obs i lämplig biotop</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2842,10 +2859,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130351270</v>
+        <v>130351258</v>
       </c>
       <c r="B24" t="n">
-        <v>58023</v>
+        <v>91776</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2853,46 +2870,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gärdsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>419298</v>
+        <v>419481</v>
       </c>
       <c r="R24" t="n">
-        <v>7019139</v>
+        <v>7019167</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,11 +2930,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>obs i lämplig biotop</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 54988-2025 artfynd.xlsx
+++ b/artfynd/A 54988-2025 artfynd.xlsx
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130351284</v>
+        <v>130351278</v>
       </c>
       <c r="B6" t="n">
-        <v>91796</v>
+        <v>91772</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,19 +1084,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1104,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>419473</v>
+        <v>419628</v>
       </c>
       <c r="R6" t="n">
-        <v>7019235</v>
+        <v>7019018</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130351278</v>
+        <v>130351284</v>
       </c>
       <c r="B7" t="n">
-        <v>91772</v>
+        <v>91796</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,23 +1181,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>419628</v>
+        <v>419473</v>
       </c>
       <c r="R7" t="n">
-        <v>7019018</v>
+        <v>7019235</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1656,7 +1656,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130351279</v>
+        <v>130351273</v>
       </c>
       <c r="B12" t="n">
         <v>91772</v>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>419412</v>
+        <v>419486</v>
       </c>
       <c r="R12" t="n">
-        <v>7019143</v>
+        <v>7019567</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130351273</v>
+        <v>130351279</v>
       </c>
       <c r="B13" t="n">
         <v>91772</v>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>419486</v>
+        <v>419412</v>
       </c>
       <c r="R13" t="n">
-        <v>7019567</v>
+        <v>7019143</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,10 +1943,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130351274</v>
+        <v>130351265</v>
       </c>
       <c r="B15" t="n">
-        <v>91772</v>
+        <v>57864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1954,21 +1954,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>419551</v>
+        <v>419404</v>
       </c>
       <c r="R15" t="n">
-        <v>7019337</v>
+        <v>7019150</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2014,6 +2014,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2040,10 +2045,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130351265</v>
+        <v>130351274</v>
       </c>
       <c r="B16" t="n">
-        <v>57864</v>
+        <v>91772</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2051,21 +2056,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2075,10 +2080,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>419404</v>
+        <v>419551</v>
       </c>
       <c r="R16" t="n">
-        <v>7019150</v>
+        <v>7019337</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2111,11 +2116,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2346,7 +2346,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130351263</v>
+        <v>130351264</v>
       </c>
       <c r="B19" t="n">
         <v>57864</v>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>419602</v>
+        <v>419527</v>
       </c>
       <c r="R19" t="n">
-        <v>7019089</v>
+        <v>7019036</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2448,7 +2448,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130351264</v>
+        <v>130351263</v>
       </c>
       <c r="B20" t="n">
         <v>57864</v>
@@ -2483,10 +2483,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>419527</v>
+        <v>419602</v>
       </c>
       <c r="R20" t="n">
-        <v>7019036</v>
+        <v>7019089</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130351283</v>
+        <v>130351267</v>
       </c>
       <c r="B21" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2561,19 +2561,23 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2581,10 +2585,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419527</v>
+        <v>419476</v>
       </c>
       <c r="R21" t="n">
-        <v>7019036</v>
+        <v>7019228</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2617,6 +2621,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2643,10 +2652,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130351267</v>
+        <v>130351258</v>
       </c>
       <c r="B22" t="n">
-        <v>57864</v>
+        <v>91776</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2654,21 +2663,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2678,10 +2687,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>419476</v>
+        <v>419481</v>
       </c>
       <c r="R22" t="n">
-        <v>7019228</v>
+        <v>7019167</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2714,11 +2723,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2745,10 +2749,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130351270</v>
+        <v>130351283</v>
       </c>
       <c r="B23" t="n">
-        <v>58023</v>
+        <v>91796</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2756,46 +2760,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gärdsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>419298</v>
+        <v>419527</v>
       </c>
       <c r="R23" t="n">
-        <v>7019139</v>
+        <v>7019036</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2828,11 +2816,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>obs i lämplig biotop</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2859,10 +2842,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130351258</v>
+        <v>130351270</v>
       </c>
       <c r="B24" t="n">
-        <v>91776</v>
+        <v>58023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2870,34 +2853,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gärdsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>419481</v>
+        <v>419298</v>
       </c>
       <c r="R24" t="n">
-        <v>7019167</v>
+        <v>7019139</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2930,6 +2925,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>obs i lämplig biotop</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3155,7 +3155,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130351281</v>
+        <v>130351277</v>
       </c>
       <c r="B27" t="n">
         <v>91772</v>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>419233</v>
+        <v>419689</v>
       </c>
       <c r="R27" t="n">
-        <v>7019867</v>
+        <v>7018949</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130351277</v>
+        <v>130351281</v>
       </c>
       <c r="B28" t="n">
         <v>91772</v>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>419689</v>
+        <v>419233</v>
       </c>
       <c r="R28" t="n">
-        <v>7018949</v>
+        <v>7019867</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 54988-2025 artfynd.xlsx
+++ b/artfynd/A 54988-2025 artfynd.xlsx
@@ -2550,10 +2550,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130351267</v>
+        <v>130351283</v>
       </c>
       <c r="B21" t="n">
-        <v>57864</v>
+        <v>91796</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2561,23 +2561,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2585,10 +2581,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419476</v>
+        <v>419527</v>
       </c>
       <c r="R21" t="n">
-        <v>7019228</v>
+        <v>7019036</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2621,11 +2617,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2749,10 +2740,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130351283</v>
+        <v>130351267</v>
       </c>
       <c r="B23" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2760,19 +2751,23 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2780,10 +2775,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>419527</v>
+        <v>419476</v>
       </c>
       <c r="R23" t="n">
-        <v>7019036</v>
+        <v>7019228</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2816,6 +2811,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 54988-2025 artfynd.xlsx
+++ b/artfynd/A 54988-2025 artfynd.xlsx
@@ -3352,7 +3352,7 @@
         <v>130351261</v>
       </c>
       <c r="B29" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 54988-2025 artfynd.xlsx
+++ b/artfynd/A 54988-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130351276</v>
+        <v>130351273</v>
       </c>
       <c r="B2" t="n">
-        <v>91772</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419580</v>
+        <v>419486</v>
       </c>
       <c r="R2" t="n">
-        <v>7019107</v>
+        <v>7019567</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130351259</v>
+        <v>130351274</v>
       </c>
       <c r="B3" t="n">
-        <v>57864</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419346</v>
+        <v>419551</v>
       </c>
       <c r="R3" t="n">
-        <v>7019843</v>
+        <v>7019337</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130351269</v>
+        <v>130351275</v>
       </c>
       <c r="B4" t="n">
-        <v>57864</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>419271</v>
+        <v>419569</v>
       </c>
       <c r="R4" t="n">
-        <v>7019829</v>
+        <v>7019293</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130351285</v>
+        <v>130351276</v>
       </c>
       <c r="B5" t="n">
-        <v>79221</v>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>419449</v>
+        <v>419580</v>
       </c>
       <c r="R5" t="n">
-        <v>7019640</v>
+        <v>7019107</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130351278</v>
+        <v>130351277</v>
       </c>
       <c r="B6" t="n">
-        <v>91772</v>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>419628</v>
+        <v>419689</v>
       </c>
       <c r="R6" t="n">
-        <v>7019018</v>
+        <v>7018949</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130351284</v>
+        <v>130351278</v>
       </c>
       <c r="B7" t="n">
-        <v>91796</v>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,19 +1171,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1201,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>419473</v>
+        <v>419628</v>
       </c>
       <c r="R7" t="n">
-        <v>7019235</v>
+        <v>7019018</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1263,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130351275</v>
+        <v>130351279</v>
       </c>
       <c r="B8" t="n">
-        <v>91772</v>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>419569</v>
+        <v>419412</v>
       </c>
       <c r="R8" t="n">
-        <v>7019293</v>
+        <v>7019143</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,7 +1357,7 @@
         <v>130351280</v>
       </c>
       <c r="B9" t="n">
-        <v>91772</v>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1457,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130351286</v>
+        <v>130351281</v>
       </c>
       <c r="B10" t="n">
-        <v>79221</v>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1468,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1492,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>419591</v>
+        <v>419233</v>
       </c>
       <c r="R10" t="n">
-        <v>7019120</v>
+        <v>7019867</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1554,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130351266</v>
+        <v>130351258</v>
       </c>
       <c r="B11" t="n">
-        <v>57864</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1565,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1589,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>419477</v>
+        <v>419481</v>
       </c>
       <c r="R11" t="n">
-        <v>7019181</v>
+        <v>7019167</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1625,11 +1619,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1656,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130351273</v>
+        <v>130351272</v>
       </c>
       <c r="B12" t="n">
-        <v>91772</v>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1667,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1691,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>419486</v>
+        <v>419480</v>
       </c>
       <c r="R12" t="n">
-        <v>7019567</v>
+        <v>7019167</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1753,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130351279</v>
+        <v>130351285</v>
       </c>
       <c r="B13" t="n">
-        <v>91772</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1788,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>419412</v>
+        <v>419449</v>
       </c>
       <c r="R13" t="n">
-        <v>7019143</v>
+        <v>7019640</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1850,30 +1839,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130351282</v>
+        <v>130351286</v>
       </c>
       <c r="B14" t="n">
-        <v>91796</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1881,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>419550</v>
+        <v>419591</v>
       </c>
       <c r="R14" t="n">
-        <v>7019136</v>
+        <v>7019120</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1943,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130351265</v>
+        <v>130351259</v>
       </c>
       <c r="B15" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1978,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>419404</v>
+        <v>419346</v>
       </c>
       <c r="R15" t="n">
-        <v>7019150</v>
+        <v>7019843</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2018,7 +2011,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2045,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130351274</v>
+        <v>130351260</v>
       </c>
       <c r="B16" t="n">
-        <v>91772</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2056,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2080,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>419551</v>
+        <v>419398</v>
       </c>
       <c r="R16" t="n">
-        <v>7019337</v>
+        <v>7019709</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2116,6 +2109,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2142,10 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130351262</v>
+        <v>130351261</v>
       </c>
       <c r="B17" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2171,16 +2169,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gärdsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>419541</v>
+        <v>419582</v>
       </c>
       <c r="R17" t="n">
-        <v>7019165</v>
+        <v>7019258</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2217,7 +2223,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål ca 2,5m upp i knäckt  gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2244,10 +2250,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130351260</v>
+        <v>130351262</v>
       </c>
       <c r="B18" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2279,10 +2285,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>419398</v>
+        <v>419541</v>
       </c>
       <c r="R18" t="n">
-        <v>7019709</v>
+        <v>7019165</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2346,10 +2352,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130351264</v>
+        <v>130351263</v>
       </c>
       <c r="B19" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2381,10 +2387,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>419527</v>
+        <v>419602</v>
       </c>
       <c r="R19" t="n">
-        <v>7019036</v>
+        <v>7019089</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2448,10 +2454,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130351263</v>
+        <v>130351264</v>
       </c>
       <c r="B20" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2483,10 +2489,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>419602</v>
+        <v>419527</v>
       </c>
       <c r="R20" t="n">
-        <v>7019089</v>
+        <v>7019036</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2550,10 +2556,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130351283</v>
+        <v>130351265</v>
       </c>
       <c r="B21" t="n">
-        <v>91796</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2561,19 +2567,23 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2581,10 +2591,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419527</v>
+        <v>419404</v>
       </c>
       <c r="R21" t="n">
-        <v>7019036</v>
+        <v>7019150</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2617,6 +2627,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2643,10 +2658,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130351258</v>
+        <v>130351266</v>
       </c>
       <c r="B22" t="n">
-        <v>91776</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2654,21 +2669,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2678,10 +2693,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>419481</v>
+        <v>419477</v>
       </c>
       <c r="R22" t="n">
-        <v>7019167</v>
+        <v>7019181</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2714,6 +2729,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2743,7 +2763,7 @@
         <v>130351267</v>
       </c>
       <c r="B23" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2842,10 +2862,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130351270</v>
+        <v>130351268</v>
       </c>
       <c r="B24" t="n">
-        <v>58023</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2853,46 +2873,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gärdsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>419298</v>
+        <v>419470</v>
       </c>
       <c r="R24" t="n">
-        <v>7019139</v>
+        <v>7019324</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2929,7 +2937,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>obs i lämplig biotop</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2956,10 +2964,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130351268</v>
+        <v>130351269</v>
       </c>
       <c r="B25" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2991,10 +2999,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>419470</v>
+        <v>419271</v>
       </c>
       <c r="R25" t="n">
-        <v>7019324</v>
+        <v>7019829</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3031,7 +3039,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3058,45 +3066,57 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130351272</v>
+        <v>130351270</v>
       </c>
       <c r="B26" t="n">
-        <v>92235</v>
+        <v>58114</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gärdsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>419480</v>
+        <v>419298</v>
       </c>
       <c r="R26" t="n">
-        <v>7019167</v>
+        <v>7019139</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3131,6 +3151,11 @@
           <t>2025-12-30</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>obs i lämplig biotop</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3152,310 +3177,6 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>130351277</v>
-      </c>
-      <c r="B27" t="n">
-        <v>91772</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Gärdsåsen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>419689</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7018949</v>
-      </c>
-      <c r="S27" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Undersåker</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>130351281</v>
-      </c>
-      <c r="B28" t="n">
-        <v>91772</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Gärdsåsen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>419233</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7019867</v>
-      </c>
-      <c r="S28" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Undersåker</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>130351261</v>
-      </c>
-      <c r="B29" t="n">
-        <v>57878</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Gärdsåsen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>419582</v>
-      </c>
-      <c r="R29" t="n">
-        <v>7019258</v>
-      </c>
-      <c r="S29" t="n">
-        <v>10</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Undersåker</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Bohål ca 2,5m upp i knäckt  gran</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54988-2025 artfynd.xlsx
+++ b/artfynd/A 54988-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351273</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351274</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351275</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351276</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351277</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351278</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351279</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351280</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351281</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351258</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351272</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351285</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351286</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351259</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2137,6 +2212,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351260</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2247,6 +2327,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351261</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2349,6 +2434,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351262</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2451,6 +2541,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351263</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2553,6 +2648,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351264</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2655,6 +2755,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351265</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2757,6 +2862,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351266</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2859,6 +2969,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351267</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2961,6 +3076,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351268</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3063,6 +3183,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351269</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3177,8 +3302,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351270</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>